--- a/verification/cases/roundtrip/formulas_database/init.xlsx
+++ b/verification/cases/roundtrip/formulas_database/init.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/database/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D04F2EC2-0BAB-A245-ADAA-6FD0CE762B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{263221DF-6848-4A87-B61B-8F4E3088B9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5220" yWindow="5980" windowWidth="31480" windowHeight="20160" xr2:uid="{AA7C4E44-7F13-CF4C-99C6-C69A0B99221E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{AA7C4E44-7F13-CF4C-99C6-C69A0B99221E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -657,7 +657,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -680,24 +680,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A70D944-CCE9-5842-A1A8-29A1A0460CB1}">
   <dimension ref="B2:I178"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="55.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>2</v>
       </c>
@@ -720,7 +720,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
@@ -743,7 +743,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
@@ -766,7 +766,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
@@ -789,7 +789,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
@@ -812,7 +812,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>18</v>
       </c>
@@ -835,7 +835,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
@@ -858,7 +858,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>20</v>
       </c>
@@ -881,7 +881,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>21</v>
       </c>
@@ -904,7 +904,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>22</v>
       </c>
@@ -927,7 +927,7 @@
         <v>5800</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>23</v>
       </c>
@@ -950,17 +950,17 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
         <v>2</v>
       </c>
@@ -983,7 +983,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
@@ -992,12 +992,12 @@
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
         <v>2</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="7"/>
       <c r="C25" s="7" t="s">
         <v>10</v>
@@ -1031,12 +1031,12 @@
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="6" t="s">
         <v>2</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7" t="s">
@@ -1070,12 +1070,12 @@
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
         <v>2</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -1109,12 +1109,12 @@
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="s">
         <v>2</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" s="7"/>
       <c r="C37" s="7" t="s">
         <v>10</v>
@@ -1150,12 +1150,12 @@
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
         <v>2</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="7"/>
       <c r="C41" s="7" t="s">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" s="7"/>
       <c r="C42" s="7" t="s">
         <v>17</v>
@@ -1200,12 +1200,12 @@
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B44" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B45" s="6" t="s">
         <v>2</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
@@ -1239,12 +1239,12 @@
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B48" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B49" s="6" t="s">
         <v>2</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="H50" s="7"/>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B52" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B53" s="6" t="s">
         <v>2</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="H54" s="7"/>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B56" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B57" s="6" t="s">
         <v>2</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B58" s="7" t="s">
         <v>39</v>
       </c>
@@ -1358,12 +1358,12 @@
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B60" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B61" s="6" t="s">
         <v>2</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B62" s="7"/>
       <c r="C62" s="7" t="s">
         <v>41</v>
@@ -1397,12 +1397,12 @@
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B64" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B65" s="6" t="s">
         <v>2</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B66" s="7" t="s">
         <v>9</v>
       </c>
@@ -1436,12 +1436,12 @@
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
     </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B69" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B70" s="8" t="s">
         <v>44</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B71" s="5" t="s">
         <v>25</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>56800</v>
       </c>
     </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B72" s="5" t="s">
         <v>45</v>
       </c>
@@ -1500,7 +1500,7 @@
         <v>21300</v>
       </c>
     </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B73" s="5" t="s">
         <v>46</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>36800</v>
       </c>
     </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B74" s="5" t="s">
         <v>47</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>36300</v>
       </c>
     </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>16300</v>
       </c>
     </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B76" s="5" t="s">
         <v>32</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>32300</v>
       </c>
     </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B77" s="5" t="s">
         <v>48</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>29300</v>
       </c>
     </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B78" s="5" t="s">
         <v>49</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>36800</v>
       </c>
     </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B79" s="5" t="s">
         <v>50</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B80" s="5" t="s">
         <v>51</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B81" s="5" t="s">
         <v>52</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B82" s="5" t="s">
         <v>53</v>
       </c>
@@ -1710,12 +1710,12 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B85" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B86" s="8" t="s">
         <v>44</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B87" s="5" t="s">
         <v>25</v>
       </c>
@@ -1753,7 +1753,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B88" s="5" t="s">
         <v>45</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>5325</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B89" s="5" t="s">
         <v>46</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>6133.333333333333</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B90" s="5" t="s">
         <v>47</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>7260</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B91" s="5" t="s">
         <v>31</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>5433.333333333333</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B92" s="5" t="s">
         <v>32</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>4614.2857142857147</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B93" s="5" t="s">
         <v>48</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>5860</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B94" s="5" t="s">
         <v>49</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>5257.1428571428569</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B95" s="5" t="s">
         <v>50</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>6666.666666666667</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B96" s="5" t="s">
         <v>51</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B97" s="5" t="s">
         <v>52</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B98" s="5" t="s">
         <v>53</v>
       </c>
@@ -1984,12 +1984,12 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B101" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B102" s="8" t="s">
         <v>44</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B103" s="5" t="s">
         <v>25</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B104" s="5" t="s">
         <v>45</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B105" s="5" t="s">
         <v>46</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B106" s="5" t="s">
         <v>47</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B107" s="5" t="s">
         <v>31</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B108" s="5" t="s">
         <v>32</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B109" s="5" t="s">
         <v>48</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B110" s="5" t="s">
         <v>49</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B111" s="5" t="s">
         <v>50</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B112" s="5" t="s">
         <v>51</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B113" s="5" t="s">
         <v>52</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B114" s="5" t="s">
         <v>53</v>
       </c>
@@ -2258,12 +2258,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B117" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B118" s="8" t="s">
         <v>44</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B119" s="5" t="s">
         <v>25</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B120" s="5" t="s">
         <v>45</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B121" s="5" t="s">
         <v>46</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B122" s="5" t="s">
         <v>47</v>
       </c>
@@ -2421,7 +2421,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B123" s="5" t="s">
         <v>31</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B124" s="5" t="s">
         <v>32</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B125" s="5" t="s">
         <v>48</v>
       </c>
@@ -2520,7 +2520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B126" s="5" t="s">
         <v>49</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B127" s="5" t="s">
         <v>50</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B128" s="5" t="s">
         <v>51</v>
       </c>
@@ -2619,7 +2619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B129" s="5" t="s">
         <v>52</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B130" s="5" t="s">
         <v>53</v>
       </c>
@@ -2685,12 +2685,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B133" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="134" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B134" t="s">
         <v>44</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B135" t="s">
         <v>25</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="136" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B136" t="s">
         <v>45</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="137" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B137" s="4" t="s">
         <v>46</v>
       </c>
@@ -2770,7 +2770,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="138" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B138" s="8" t="s">
         <v>47</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="139" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B139" s="5" t="s">
         <v>31</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="140" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B140" s="5" t="s">
         <v>32</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="141" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B141" s="5" t="s">
         <v>48</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B142" s="5" t="s">
         <v>49</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="143" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B143" s="5" t="s">
         <v>50</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="144" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B144" s="5" t="s">
         <v>51</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B145" s="5" t="s">
         <v>52</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B146" s="5" t="s">
         <v>53</v>
       </c>
@@ -2959,21 +2959,21 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B147" s="5"/>
       <c r="C147" s="9"/>
       <c r="D147" s="9"/>
       <c r="E147" s="9"/>
       <c r="F147" s="9"/>
     </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B148" s="5"/>
       <c r="C148" s="9"/>
       <c r="D148" s="9"/>
       <c r="E148" s="9"/>
       <c r="F148" s="9"/>
     </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B149" s="5" t="s">
         <v>58</v>
       </c>
@@ -2982,7 +2982,7 @@
       <c r="E149" s="9"/>
       <c r="F149" s="9"/>
     </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B150" s="5" t="s">
         <v>44</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
         <v>25</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
         <v>45</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="153" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B153" s="4" t="s">
         <v>46</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="154" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B154" s="8" t="s">
         <v>47</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>5800</v>
       </c>
     </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B155" s="5" t="s">
         <v>31</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B156" s="5" t="s">
         <v>32</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B157" s="5" t="s">
         <v>48</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B158" s="5" t="s">
         <v>49</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B159" s="5" t="s">
         <v>50</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B160" s="5" t="s">
         <v>51</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="161" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B161" s="5" t="s">
         <v>52</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B162" s="5" t="s">
         <v>53</v>
       </c>
@@ -3251,21 +3251,21 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="163" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B163" s="5"/>
       <c r="C163" s="9"/>
       <c r="D163" s="9"/>
       <c r="E163" s="9"/>
       <c r="F163" s="9"/>
     </row>
-    <row r="164" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B164" s="5"/>
       <c r="C164" s="9"/>
       <c r="D164" s="9"/>
       <c r="E164" s="9"/>
       <c r="F164" s="9"/>
     </row>
-    <row r="165" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B165" s="5" t="s">
         <v>59</v>
       </c>
@@ -3274,7 +3274,7 @@
       <c r="E165" s="9"/>
       <c r="F165" s="9"/>
     </row>
-    <row r="166" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B166" s="8" t="s">
         <v>44</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="167" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B167" s="5" t="s">
         <v>25</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="168" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="168" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B168" s="5" t="s">
         <v>45</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="169" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="169" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B169" s="5" t="s">
         <v>46</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="170" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B170" s="5" t="s">
         <v>47</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="171" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B171" s="5" t="s">
         <v>31</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="172" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B172" s="5" t="s">
         <v>32</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="173" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B173" s="5" t="s">
         <v>48</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="174" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="174" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B174" s="5" t="s">
         <v>49</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="175" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B175" s="5" t="s">
         <v>50</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="176" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B176" s="5" t="s">
         <v>51</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="177" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B177" s="5" t="s">
         <v>52</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="178" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B178" s="5" t="s">
         <v>53</v>
       </c>
